--- a/pcb/JLCPCB_2layers_simplified/xiao_linefollower/production_2layer/lioncircuits/CPL_Lion.xlsx
+++ b/pcb/JLCPCB_2layers_simplified/xiao_linefollower/production_2layer/lioncircuits/CPL_Lion.xlsx
@@ -40,17 +40,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">U3</t>
+          <t xml:space="preserve">R24</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">50mm</t>
+          <t xml:space="preserve">52.19mm</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">109.3725mm</t>
+          <t xml:space="preserve">58mm</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -60,24 +60,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">270</t>
+          <t xml:space="preserve">180</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">D33</t>
+          <t xml:space="preserve">U3</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31.5mm</t>
+          <t xml:space="preserve">50mm</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111mm</t>
+          <t xml:space="preserve">109.3725mm</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -87,7 +87,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">270</t>
         </is>
       </c>
     </row>
@@ -121,17 +121,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">D54</t>
+          <t xml:space="preserve">L1</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">18.8mm</t>
+          <t xml:space="preserve">33.7mm</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">41.07mm</t>
+          <t xml:space="preserve">95.4mm</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -148,17 +148,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">L1</t>
+          <t xml:space="preserve">Q3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">33.7mm</t>
+          <t xml:space="preserve">70.32mm</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">95.4mm</t>
+          <t xml:space="preserve">21.6mm</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -175,17 +175,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q3</t>
+          <t xml:space="preserve">R1</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">67.78mm</t>
+          <t xml:space="preserve">72.5mm</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">24mm</t>
+          <t xml:space="preserve">114.31mm</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -195,24 +195,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">180</t>
+          <t xml:space="preserve">270</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">R81</t>
+          <t xml:space="preserve">R55</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">58.5mm</t>
+          <t xml:space="preserve">37.13mm</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">47mm</t>
+          <t xml:space="preserve">33.26mm</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -222,24 +222,24 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t xml:space="preserve">270</t>
+          <t xml:space="preserve">180</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">R82</t>
+          <t xml:space="preserve">R15</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">26mm</t>
+          <t xml:space="preserve">59.19mm</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">108mm</t>
+          <t xml:space="preserve">21mm</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -249,24 +249,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">180</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">R108</t>
+          <t xml:space="preserve">J1</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">67.82mm</t>
+          <t xml:space="preserve">88.25mm</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">43.08mm</t>
+          <t xml:space="preserve">105mm</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -283,17 +283,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">J1</t>
+          <t xml:space="preserve">D4</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">88.25mm</t>
+          <t xml:space="preserve">74.348mm</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">105mm</t>
+          <t xml:space="preserve">35.548mm</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -303,24 +303,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">315</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">R55</t>
+          <t xml:space="preserve">C14</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">41mm</t>
+          <t xml:space="preserve">58mm</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">47mm</t>
+          <t xml:space="preserve">37.5mm</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -337,17 +337,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">D4</t>
+          <t xml:space="preserve">SW6</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">74.348mm</t>
+          <t xml:space="preserve">11.75mm</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">35.548mm</t>
+          <t xml:space="preserve">116.07mm</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -357,24 +357,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">315</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">C14</t>
+          <t xml:space="preserve">D1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">58mm</t>
+          <t xml:space="preserve">21.13mm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">37.5mm</t>
+          <t xml:space="preserve">21.6mm</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -384,24 +384,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">180</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">D1</t>
+          <t xml:space="preserve">R17</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">21.13mm</t>
+          <t xml:space="preserve">22.81mm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">21.6mm</t>
+          <t xml:space="preserve">48mm</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -411,7 +411,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">180</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
@@ -445,17 +445,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">U5</t>
+          <t xml:space="preserve">R69</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">70.5mm</t>
+          <t xml:space="preserve">80mm</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">94mm</t>
+          <t xml:space="preserve">98.19mm</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -465,24 +465,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">90</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">R104</t>
+          <t xml:space="preserve">R21</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">33.5mm</t>
+          <t xml:space="preserve">18.81mm</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">105mm</t>
+          <t xml:space="preserve">53mm</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -499,17 +499,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">R1</t>
+          <t xml:space="preserve">R19</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">72.5mm</t>
+          <t xml:space="preserve">71.19mm</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">111.5mm</t>
+          <t xml:space="preserve">45mm</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -519,24 +519,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">180</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">D52</t>
+          <t xml:space="preserve">SW2</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">32.18mm</t>
+          <t xml:space="preserve">90.1mm</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">40.88mm</t>
+          <t xml:space="preserve">98.8mm</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -553,17 +553,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">D50</t>
+          <t xml:space="preserve">D29</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">34.95mm</t>
+          <t xml:space="preserve">50mm</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">24mm</t>
+          <t xml:space="preserve">42mm</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -573,24 +573,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">90</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">C50</t>
+          <t xml:space="preserve">F1</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">71mm</t>
+          <t xml:space="preserve">34.5mm</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">101.5mm</t>
+          <t xml:space="preserve">37.5mm</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -607,17 +607,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">D29</t>
+          <t xml:space="preserve">D5</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">50mm</t>
+          <t xml:space="preserve">13.5mm</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">42mm</t>
+          <t xml:space="preserve">44.2mm</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -634,17 +634,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">D53</t>
+          <t xml:space="preserve">R13</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">67.82mm</t>
+          <t xml:space="preserve">40.81mm</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">40.88mm</t>
+          <t xml:space="preserve">21mm</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -661,17 +661,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">R110</t>
+          <t xml:space="preserve">J5</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">77.0971mm</t>
+          <t xml:space="preserve">36.25mm</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">42.6595mm</t>
+          <t xml:space="preserve">52.5mm</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -688,17 +688,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">F1</t>
+          <t xml:space="preserve">C12</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t xml:space="preserve">34.5mm</t>
+          <t xml:space="preserve">50mm</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">37.5mm</t>
+          <t xml:space="preserve">46mm</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -715,17 +715,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">D5</t>
+          <t xml:space="preserve">C5</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">13.5mm</t>
+          <t xml:space="preserve">59mm</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">44.2mm</t>
+          <t xml:space="preserve">43.5mm</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -735,24 +735,24 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t xml:space="preserve">90</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">SW6</t>
+          <t xml:space="preserve">U2</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">6mm</t>
+          <t xml:space="preserve">47mm</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">116mm</t>
+          <t xml:space="preserve">31mm</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -769,17 +769,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">C30</t>
+          <t xml:space="preserve">R18</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">37mm</t>
+          <t xml:space="preserve">28mm</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">31.5mm</t>
+          <t xml:space="preserve">55.81mm</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -789,24 +789,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">270</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">J5</t>
+          <t xml:space="preserve">R22</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">36.25mm</t>
+          <t xml:space="preserve">35.81mm</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">52.5mm</t>
+          <t xml:space="preserve">58mm</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -823,17 +823,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">L2</t>
+          <t xml:space="preserve">C4</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">84.7mm</t>
+          <t xml:space="preserve">65.5mm</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">99.3mm</t>
+          <t xml:space="preserve">37mm</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -850,17 +850,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">D55</t>
+          <t xml:space="preserve">Q17</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">81.2mm</t>
+          <t xml:space="preserve">50mm</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">41.07mm</t>
+          <t xml:space="preserve">37.5mm</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -877,7 +877,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">C12</t>
+          <t xml:space="preserve">C3</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -887,7 +887,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">46mm</t>
+          <t xml:space="preserve">48.5mm</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -904,17 +904,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">R105</t>
+          <t xml:space="preserve">J6</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">44.0187mm</t>
+          <t xml:space="preserve">63.5mm</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">24.047mm</t>
+          <t xml:space="preserve">53.5mm</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -924,24 +924,24 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">180</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">C5</t>
+          <t xml:space="preserve">R14</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">59mm</t>
+          <t xml:space="preserve">22.81mm</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">43.5mm</t>
+          <t xml:space="preserve">43mm</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -958,17 +958,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">SW7</t>
+          <t xml:space="preserve">Q1</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">68.4mm</t>
+          <t xml:space="preserve">34mm</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">116.5mm</t>
+          <t xml:space="preserve">101.1mm</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -985,17 +985,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">U2</t>
+          <t xml:space="preserve">D3</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">47mm</t>
+          <t xml:space="preserve">25.648mm</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">31mm</t>
+          <t xml:space="preserve">35.552mm</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1005,24 +1005,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4</t>
+          <t xml:space="preserve">Q16</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">65.5mm</t>
+          <t xml:space="preserve">40mm</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">37mm</t>
+          <t xml:space="preserve">37.5mm</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1039,17 +1039,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">R109</t>
+          <t xml:space="preserve">R62</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">22.9029mm</t>
+          <t xml:space="preserve">45mm</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">42.6595mm</t>
+          <t xml:space="preserve">41.31mm</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1059,24 +1059,24 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">270</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q17</t>
+          <t xml:space="preserve">R20</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">50mm</t>
+          <t xml:space="preserve">72mm</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">37.5mm</t>
+          <t xml:space="preserve">55.81mm</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1086,24 +1086,24 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">270</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">C3</t>
+          <t xml:space="preserve">R82</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">50mm</t>
+          <t xml:space="preserve">29.81mm</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">48.5mm</t>
+          <t xml:space="preserve">108mm</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1120,17 +1120,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">SW2</t>
+          <t xml:space="preserve">C11</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">90.5168mm</t>
+          <t xml:space="preserve">65.5mm</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">98.4135mm</t>
+          <t xml:space="preserve">33mm</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1147,17 +1147,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">J6</t>
+          <t xml:space="preserve">C2</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">63.5mm</t>
+          <t xml:space="preserve">41mm</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">53.5mm</t>
+          <t xml:space="preserve">44.5mm</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1167,24 +1167,24 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">180</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q1</t>
+          <t xml:space="preserve">Q7</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">34mm</t>
+          <t xml:space="preserve">85mm</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">101.1mm</t>
+          <t xml:space="preserve">36.59mm</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1194,24 +1194,24 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">270</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">D3</t>
+          <t xml:space="preserve">D30</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">25.648mm</t>
+          <t xml:space="preserve">22mm</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">35.552mm</t>
+          <t xml:space="preserve">107.75mm</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1221,24 +1221,24 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q16</t>
+          <t xml:space="preserve">Q18</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">40mm</t>
+          <t xml:space="preserve">68mm</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">37.5mm</t>
+          <t xml:space="preserve">110mm</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1255,17 +1255,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">C11</t>
+          <t xml:space="preserve">SW1</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">65.5mm</t>
+          <t xml:space="preserve">90.1mm</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">33mm</t>
+          <t xml:space="preserve">91.8mm</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1282,17 +1282,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">C2</t>
+          <t xml:space="preserve">Q5</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">41mm</t>
+          <t xml:space="preserve">79.718mm</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">44.5mm</t>
+          <t xml:space="preserve">30.178mm</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1302,24 +1302,24 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">315</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">R107</t>
+          <t xml:space="preserve">D2</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">32.18mm</t>
+          <t xml:space="preserve">78.87mm</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">43.08mm</t>
+          <t xml:space="preserve">21.6mm</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1336,17 +1336,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">D51</t>
+          <t xml:space="preserve">D6</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">62.45mm</t>
+          <t xml:space="preserve">86.5mm</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">24mm</t>
+          <t xml:space="preserve">44.19mm</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1356,24 +1356,24 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">270</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q7</t>
+          <t xml:space="preserve">Q34</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">85mm</t>
+          <t xml:space="preserve">21.5mm</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">36.6mm</t>
+          <t xml:space="preserve">111mm</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1383,24 +1383,24 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">270</t>
+          <t xml:space="preserve">180</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">D30</t>
+          <t xml:space="preserve">C8</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">22mm</t>
+          <t xml:space="preserve">66.5mm</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">107.75mm</t>
+          <t xml:space="preserve">105.75mm</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1410,24 +1410,24 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">90</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">R106</t>
+          <t xml:space="preserve">R16</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">58.7545mm</t>
+          <t xml:space="preserve">79mm</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">22.4693mm</t>
+          <t xml:space="preserve">47.81mm</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1437,24 +1437,24 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">270</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">R103</t>
+          <t xml:space="preserve">R23</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">23mm</t>
+          <t xml:space="preserve">64.19mm</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t xml:space="preserve">102mm</t>
+          <t xml:space="preserve">58mm</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -1464,24 +1464,24 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">180</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q18</t>
+          <t xml:space="preserve">Q6</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">68mm</t>
+          <t xml:space="preserve">15mm</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">110mm</t>
+          <t xml:space="preserve">36.6mm</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -1491,24 +1491,24 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">90</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">SW1</t>
+          <t xml:space="preserve">J10</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">90.1mm</t>
+          <t xml:space="preserve">86.6mm</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">91.8mm</t>
+          <t xml:space="preserve">114.5mm</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -1525,17 +1525,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q5</t>
+          <t xml:space="preserve">Q2</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">79.718mm</t>
+          <t xml:space="preserve">29.68mm</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">30.178mm</t>
+          <t xml:space="preserve">21.6mm</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -1545,24 +1545,24 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t xml:space="preserve">315</t>
+          <t xml:space="preserve">180</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">D2</t>
+          <t xml:space="preserve">Q4</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">74.73mm</t>
+          <t xml:space="preserve">20.278mm</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">24mm</t>
+          <t xml:space="preserve">30.182mm</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -1572,24 +1572,24 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">180</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">D6</t>
+          <t xml:space="preserve">SW5</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">86.5mm</t>
+          <t xml:space="preserve">26mm</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">44.2mm</t>
+          <t xml:space="preserve">116.5mm</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -1599,24 +1599,24 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t xml:space="preserve">270</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q34</t>
+          <t xml:space="preserve">R63</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">21.5mm</t>
+          <t xml:space="preserve">54mm</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">111mm</t>
+          <t xml:space="preserve">45.31mm</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -1626,24 +1626,24 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">180</t>
+          <t xml:space="preserve">270</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">C8</t>
+          <t xml:space="preserve">C1</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">66.5mm</t>
+          <t xml:space="preserve">39.5mm</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">105.75mm</t>
+          <t xml:space="preserve">25.5mm</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -1653,24 +1653,24 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">90</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q6</t>
+          <t xml:space="preserve">U1</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">15mm</t>
+          <t xml:space="preserve">34mm</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">36.6mm</t>
+          <t xml:space="preserve">114mm</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -1680,24 +1680,24 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">90</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">J10</t>
+          <t xml:space="preserve">R64</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">86.6mm</t>
+          <t xml:space="preserve">34.19mm</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">114.5mm</t>
+          <t xml:space="preserve">48mm</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -1707,24 +1707,24 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">180</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q2</t>
+          <t xml:space="preserve">R81</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">29.68mm</t>
+          <t xml:space="preserve">63.5mm</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">24mm</t>
+          <t xml:space="preserve">44.81mm</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -1734,952 +1734,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">180</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Q4</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20.278mm</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30.182mm</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Top</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">45</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">SW5</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26mm</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">116.5mm</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Top</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R84</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">32mm</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108mm</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Top</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C1</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">39.5mm</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25.5mm</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Top</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">U1</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">34mm</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114mm</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Top</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">U7</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29.5mm</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101mm</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Top</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">0</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R18</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30mm</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30mm</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bottom</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R8</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19mm</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102.6mm</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bottom</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R15</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96mm</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101mm</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bottom</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R9</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38.8mm</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">93mm</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bottom</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R6</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20mm</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">105mm</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bottom</t>
-        </is>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R17</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26mm</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30mm</t>
-        </is>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bottom</t>
-        </is>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R20</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">70mm</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30mm</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bottom</t>
-        </is>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R62</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">44mm</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">37.5mm</t>
-        </is>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bottom</t>
-        </is>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R16</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">91.5mm</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">95mm</t>
-        </is>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bottom</t>
-        </is>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R23</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96mm</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">95mm</t>
-        </is>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bottom</t>
-        </is>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R24</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96mm</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98mm</t>
-        </is>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bottom</t>
-        </is>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R19</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">74mm</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">30mm</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bottom</t>
-        </is>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R21</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4mm</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">101mm</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bottom</t>
-        </is>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R74</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19mm</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">93mm</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bottom</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R13</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4mm</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98mm</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bottom</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C16</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">92.6mm</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">45.1mm</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bottom</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R22</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8.5mm</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">95mm</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bottom</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R85</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">77.5mm</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">105mm</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bottom</t>
-        </is>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R14</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4mm</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">95mm</t>
-        </is>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bottom</t>
-        </is>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R71</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">62mm</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">41mm</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bottom</t>
-        </is>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C15</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72.1mm</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108.6mm</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bottom</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R64</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">44mm</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">42mm</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bottom</t>
-        </is>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R73</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">61.3mm</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">93mm</t>
-        </is>
-      </c>
-      <c r="D93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bottom</t>
-        </is>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C17</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">66.4mm</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102mm</t>
-        </is>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bottom</t>
-        </is>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">C18</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">72mm</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">105.5mm</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bottom</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R63</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">54mm</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">37.5mm</t>
-        </is>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bottom</t>
-        </is>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R7</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27mm</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">105mm</t>
-        </is>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bottom</t>
-        </is>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R70</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">58mm</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">41mm</t>
-        </is>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bottom</t>
-        </is>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">R69</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80mm</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">102mm</t>
-        </is>
-      </c>
-      <c r="D99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bottom</t>
-        </is>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180</t>
+          <t xml:space="preserve">270</t>
         </is>
       </c>
     </row>

--- a/pcb/JLCPCB_2layers_simplified/xiao_linefollower/production_2layer/lioncircuits/CPL_Lion.xlsx
+++ b/pcb/JLCPCB_2layers_simplified/xiao_linefollower/production_2layer/lioncircuits/CPL_Lion.xlsx
@@ -40,17 +40,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">R24</t>
+          <t xml:space="preserve">U3</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t xml:space="preserve">52.19mm</t>
+          <t xml:space="preserve">50mm</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t xml:space="preserve">58mm</t>
+          <t xml:space="preserve">109.3725mm</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -60,24 +60,24 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t xml:space="preserve">180</t>
+          <t xml:space="preserve">270</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">U3</t>
+          <t xml:space="preserve">C10</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50mm</t>
+          <t xml:space="preserve">75.1mm</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109.3725mm</t>
+          <t xml:space="preserve">102.3mm</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -87,24 +87,24 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">C10</t>
+          <t xml:space="preserve">L1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">75.1mm</t>
+          <t xml:space="preserve">33.7mm</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">102.3mm</t>
+          <t xml:space="preserve">95.4mm</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -121,17 +121,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">L1</t>
+          <t xml:space="preserve">Q3</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t xml:space="preserve">33.7mm</t>
+          <t xml:space="preserve">70.32mm</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t xml:space="preserve">95.4mm</t>
+          <t xml:space="preserve">21.6mm</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -148,17 +148,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q3</t>
+          <t xml:space="preserve">R1</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t xml:space="preserve">70.32mm</t>
+          <t xml:space="preserve">72.5mm</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t xml:space="preserve">21.6mm</t>
+          <t xml:space="preserve">114.31mm</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -168,24 +168,24 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">270</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">R1</t>
+          <t xml:space="preserve">R55</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t xml:space="preserve">72.5mm</t>
+          <t xml:space="preserve">37.13mm</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">114.31mm</t>
+          <t xml:space="preserve">33.26mm</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -195,24 +195,24 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t xml:space="preserve">270</t>
+          <t xml:space="preserve">180</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">R55</t>
+          <t xml:space="preserve">R15</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t xml:space="preserve">37.13mm</t>
+          <t xml:space="preserve">59.19mm</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t xml:space="preserve">33.26mm</t>
+          <t xml:space="preserve">21mm</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -229,17 +229,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">R15</t>
+          <t xml:space="preserve">J1</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t xml:space="preserve">59.19mm</t>
+          <t xml:space="preserve">88.25mm</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t xml:space="preserve">21mm</t>
+          <t xml:space="preserve">105mm</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -249,24 +249,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t xml:space="preserve">180</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">J1</t>
+          <t xml:space="preserve">D4</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t xml:space="preserve">88.25mm</t>
+          <t xml:space="preserve">74.348mm</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t xml:space="preserve">105mm</t>
+          <t xml:space="preserve">35.548mm</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -276,24 +276,24 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">315</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">D4</t>
+          <t xml:space="preserve">C14</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t xml:space="preserve">74.348mm</t>
+          <t xml:space="preserve">58mm</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t xml:space="preserve">35.548mm</t>
+          <t xml:space="preserve">37.5mm</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -303,24 +303,24 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t xml:space="preserve">315</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">C14</t>
+          <t xml:space="preserve">SW6</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t xml:space="preserve">58mm</t>
+          <t xml:space="preserve">11.75mm</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t xml:space="preserve">37.5mm</t>
+          <t xml:space="preserve">116.07mm</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -337,17 +337,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">SW6</t>
+          <t xml:space="preserve">D1</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t xml:space="preserve">11.75mm</t>
+          <t xml:space="preserve">21.13mm</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t xml:space="preserve">116.07mm</t>
+          <t xml:space="preserve">21.6mm</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -357,24 +357,24 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">180</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">D1</t>
+          <t xml:space="preserve">BZ1</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t xml:space="preserve">21.13mm</t>
+          <t xml:space="preserve">57.5mm</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t xml:space="preserve">21.6mm</t>
+          <t xml:space="preserve">31mm</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -384,24 +384,24 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t xml:space="preserve">180</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">R17</t>
+          <t xml:space="preserve">R69</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t xml:space="preserve">22.81mm</t>
+          <t xml:space="preserve">80mm</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t xml:space="preserve">48mm</t>
+          <t xml:space="preserve">98.19mm</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -411,24 +411,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">90</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">BZ1</t>
+          <t xml:space="preserve">SW2</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t xml:space="preserve">57.5mm</t>
+          <t xml:space="preserve">90.1mm</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t xml:space="preserve">31mm</t>
+          <t xml:space="preserve">98.8mm</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -445,17 +445,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">R69</t>
+          <t xml:space="preserve">D29</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t xml:space="preserve">80mm</t>
+          <t xml:space="preserve">50mm</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t xml:space="preserve">98.19mm</t>
+          <t xml:space="preserve">42mm</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -472,17 +472,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">R21</t>
+          <t xml:space="preserve">F1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t xml:space="preserve">18.81mm</t>
+          <t xml:space="preserve">34.5mm</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t xml:space="preserve">53mm</t>
+          <t xml:space="preserve">37.5mm</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -499,17 +499,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">R19</t>
+          <t xml:space="preserve">D5</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t xml:space="preserve">71.19mm</t>
+          <t xml:space="preserve">13.5mm</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t xml:space="preserve">45mm</t>
+          <t xml:space="preserve">44.2mm</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -519,24 +519,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t xml:space="preserve">180</t>
+          <t xml:space="preserve">90</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">SW2</t>
+          <t xml:space="preserve">R13</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t xml:space="preserve">90.1mm</t>
+          <t xml:space="preserve">40.81mm</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t xml:space="preserve">98.8mm</t>
+          <t xml:space="preserve">21mm</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -553,17 +553,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">D29</t>
+          <t xml:space="preserve">J5</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t xml:space="preserve">50mm</t>
+          <t xml:space="preserve">36.25mm</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t xml:space="preserve">42mm</t>
+          <t xml:space="preserve">52.5mm</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -573,24 +573,24 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t xml:space="preserve">90</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">F1</t>
+          <t xml:space="preserve">C12</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t xml:space="preserve">34.5mm</t>
+          <t xml:space="preserve">50mm</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t xml:space="preserve">37.5mm</t>
+          <t xml:space="preserve">46mm</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -607,17 +607,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">D5</t>
+          <t xml:space="preserve">C5</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t xml:space="preserve">13.5mm</t>
+          <t xml:space="preserve">59mm</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t xml:space="preserve">44.2mm</t>
+          <t xml:space="preserve">43.5mm</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -627,24 +627,24 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t xml:space="preserve">90</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">R13</t>
+          <t xml:space="preserve">U2</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t xml:space="preserve">40.81mm</t>
+          <t xml:space="preserve">47mm</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t xml:space="preserve">21mm</t>
+          <t xml:space="preserve">31mm</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -661,17 +661,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">J5</t>
+          <t xml:space="preserve">C4</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t xml:space="preserve">36.25mm</t>
+          <t xml:space="preserve">65.5mm</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t xml:space="preserve">52.5mm</t>
+          <t xml:space="preserve">37mm</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -688,7 +688,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">C12</t>
+          <t xml:space="preserve">Q17</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -698,7 +698,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t xml:space="preserve">46mm</t>
+          <t xml:space="preserve">37.5mm</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -715,17 +715,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">C5</t>
+          <t xml:space="preserve">C3</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t xml:space="preserve">59mm</t>
+          <t xml:space="preserve">50mm</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t xml:space="preserve">43.5mm</t>
+          <t xml:space="preserve">48.5mm</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -742,17 +742,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">U2</t>
+          <t xml:space="preserve">J6</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t xml:space="preserve">47mm</t>
+          <t xml:space="preserve">63.5mm</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t xml:space="preserve">31mm</t>
+          <t xml:space="preserve">53.5mm</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -762,24 +762,24 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">180</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">R18</t>
+          <t xml:space="preserve">Q1</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t xml:space="preserve">28mm</t>
+          <t xml:space="preserve">34mm</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t xml:space="preserve">55.81mm</t>
+          <t xml:space="preserve">101.1mm</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -789,24 +789,24 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t xml:space="preserve">270</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">R22</t>
+          <t xml:space="preserve">D3</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t xml:space="preserve">35.81mm</t>
+          <t xml:space="preserve">25.648mm</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t xml:space="preserve">58mm</t>
+          <t xml:space="preserve">35.552mm</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -816,24 +816,24 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">C4</t>
+          <t xml:space="preserve">Q16</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t xml:space="preserve">65.5mm</t>
+          <t xml:space="preserve">40mm</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t xml:space="preserve">37mm</t>
+          <t xml:space="preserve">37.5mm</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -850,17 +850,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q17</t>
+          <t xml:space="preserve">R62</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t xml:space="preserve">50mm</t>
+          <t xml:space="preserve">45mm</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t xml:space="preserve">37.5mm</t>
+          <t xml:space="preserve">41.31mm</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -870,24 +870,24 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">270</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">C3</t>
+          <t xml:space="preserve">R82</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t xml:space="preserve">50mm</t>
+          <t xml:space="preserve">29.81mm</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t xml:space="preserve">48.5mm</t>
+          <t xml:space="preserve">108mm</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -904,17 +904,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">J6</t>
+          <t xml:space="preserve">C11</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t xml:space="preserve">63.5mm</t>
+          <t xml:space="preserve">65.5mm</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t xml:space="preserve">53.5mm</t>
+          <t xml:space="preserve">33mm</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -924,24 +924,24 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t xml:space="preserve">180</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">R14</t>
+          <t xml:space="preserve">C2</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t xml:space="preserve">22.81mm</t>
+          <t xml:space="preserve">41mm</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t xml:space="preserve">43mm</t>
+          <t xml:space="preserve">44.5mm</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -958,17 +958,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q1</t>
+          <t xml:space="preserve">Q7</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t xml:space="preserve">34mm</t>
+          <t xml:space="preserve">85mm</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t xml:space="preserve">101.1mm</t>
+          <t xml:space="preserve">36.59mm</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -978,24 +978,24 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">270</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">D3</t>
+          <t xml:space="preserve">D30</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t xml:space="preserve">25.648mm</t>
+          <t xml:space="preserve">22mm</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t xml:space="preserve">35.552mm</t>
+          <t xml:space="preserve">107.75mm</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -1005,24 +1005,24 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q16</t>
+          <t xml:space="preserve">Q18</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t xml:space="preserve">40mm</t>
+          <t xml:space="preserve">68mm</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t xml:space="preserve">37.5mm</t>
+          <t xml:space="preserve">110mm</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -1039,17 +1039,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">R62</t>
+          <t xml:space="preserve">SW1</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t xml:space="preserve">45mm</t>
+          <t xml:space="preserve">90.1mm</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t xml:space="preserve">41.31mm</t>
+          <t xml:space="preserve">91.8mm</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -1059,24 +1059,24 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t xml:space="preserve">270</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">R20</t>
+          <t xml:space="preserve">Q5</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t xml:space="preserve">72mm</t>
+          <t xml:space="preserve">79.718mm</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t xml:space="preserve">55.81mm</t>
+          <t xml:space="preserve">30.178mm</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -1086,24 +1086,24 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t xml:space="preserve">270</t>
+          <t xml:space="preserve">315</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">R82</t>
+          <t xml:space="preserve">D2</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t xml:space="preserve">29.81mm</t>
+          <t xml:space="preserve">78.87mm</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t xml:space="preserve">108mm</t>
+          <t xml:space="preserve">21.6mm</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -1120,17 +1120,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">C11</t>
+          <t xml:space="preserve">D6</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t xml:space="preserve">65.5mm</t>
+          <t xml:space="preserve">86.5mm</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t xml:space="preserve">33mm</t>
+          <t xml:space="preserve">44.19mm</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -1140,24 +1140,24 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">270</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">C2</t>
+          <t xml:space="preserve">Q34</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t xml:space="preserve">41mm</t>
+          <t xml:space="preserve">21.5mm</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t xml:space="preserve">44.5mm</t>
+          <t xml:space="preserve">111mm</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -1167,24 +1167,24 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">180</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q7</t>
+          <t xml:space="preserve">C8</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t xml:space="preserve">85mm</t>
+          <t xml:space="preserve">66.5mm</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t xml:space="preserve">36.59mm</t>
+          <t xml:space="preserve">105.75mm</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -1194,24 +1194,24 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t xml:space="preserve">270</t>
+          <t xml:space="preserve">90</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">D30</t>
+          <t xml:space="preserve">Q6</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t xml:space="preserve">22mm</t>
+          <t xml:space="preserve">15mm</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t xml:space="preserve">107.75mm</t>
+          <t xml:space="preserve">36.6mm</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -1221,24 +1221,24 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">90</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q18</t>
+          <t xml:space="preserve">J10</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t xml:space="preserve">68mm</t>
+          <t xml:space="preserve">86.6mm</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t xml:space="preserve">110mm</t>
+          <t xml:space="preserve">114.5mm</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -1255,17 +1255,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">SW1</t>
+          <t xml:space="preserve">Q2</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t xml:space="preserve">90.1mm</t>
+          <t xml:space="preserve">29.68mm</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t xml:space="preserve">91.8mm</t>
+          <t xml:space="preserve">21.6mm</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -1275,24 +1275,24 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">180</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q5</t>
+          <t xml:space="preserve">Q4</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t xml:space="preserve">79.718mm</t>
+          <t xml:space="preserve">20.278mm</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t xml:space="preserve">30.178mm</t>
+          <t xml:space="preserve">30.182mm</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -1302,24 +1302,24 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t xml:space="preserve">315</t>
+          <t xml:space="preserve">45</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">D2</t>
+          <t xml:space="preserve">SW5</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t xml:space="preserve">78.87mm</t>
+          <t xml:space="preserve">26mm</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t xml:space="preserve">21.6mm</t>
+          <t xml:space="preserve">116.5mm</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -1336,17 +1336,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">D6</t>
+          <t xml:space="preserve">R63</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t xml:space="preserve">86.5mm</t>
+          <t xml:space="preserve">54mm</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t xml:space="preserve">44.19mm</t>
+          <t xml:space="preserve">45.31mm</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -1363,17 +1363,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q34</t>
+          <t xml:space="preserve">C1</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t xml:space="preserve">21.5mm</t>
+          <t xml:space="preserve">39.5mm</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t xml:space="preserve">111mm</t>
+          <t xml:space="preserve">25.5mm</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -1383,24 +1383,24 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t xml:space="preserve">180</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">C8</t>
+          <t xml:space="preserve">U1</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t xml:space="preserve">66.5mm</t>
+          <t xml:space="preserve">34mm</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t xml:space="preserve">105.75mm</t>
+          <t xml:space="preserve">114mm</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -1410,24 +1410,24 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t xml:space="preserve">90</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">R16</t>
+          <t xml:space="preserve">R81</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">79mm</t>
+          <t xml:space="preserve">63.5mm</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t xml:space="preserve">47.81mm</t>
+          <t xml:space="preserve">44.81mm</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -1444,12 +1444,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">R23</t>
+          <t xml:space="preserve">R24</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t xml:space="preserve">64.19mm</t>
+          <t xml:space="preserve">52.19mm</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1459,7 +1459,7 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -1471,49 +1471,49 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q6</t>
+          <t xml:space="preserve">R17</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t xml:space="preserve">15mm</t>
+          <t xml:space="preserve">22.81mm</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t xml:space="preserve">36.6mm</t>
+          <t xml:space="preserve">48mm</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t xml:space="preserve">90</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">J10</t>
+          <t xml:space="preserve">R21</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t xml:space="preserve">86.6mm</t>
+          <t xml:space="preserve">18.81mm</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t xml:space="preserve">114.5mm</t>
+          <t xml:space="preserve">53mm</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -1525,22 +1525,22 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q2</t>
+          <t xml:space="preserve">R19</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t xml:space="preserve">29.68mm</t>
+          <t xml:space="preserve">71.19mm</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t xml:space="preserve">21.6mm</t>
+          <t xml:space="preserve">45mm</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -1552,49 +1552,49 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Q4</t>
+          <t xml:space="preserve">R18</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t xml:space="preserve">20.278mm</t>
+          <t xml:space="preserve">28mm</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t xml:space="preserve">30.182mm</t>
+          <t xml:space="preserve">55.81mm</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t xml:space="preserve">45</t>
+          <t xml:space="preserve">270</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">SW5</t>
+          <t xml:space="preserve">R22</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t xml:space="preserve">26mm</t>
+          <t xml:space="preserve">35.81mm</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t xml:space="preserve">116.5mm</t>
+          <t xml:space="preserve">58mm</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -1606,103 +1606,103 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">R63</t>
+          <t xml:space="preserve">R14</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t xml:space="preserve">54mm</t>
+          <t xml:space="preserve">22.81mm</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t xml:space="preserve">45.31mm</t>
+          <t xml:space="preserve">43mm</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t xml:space="preserve">270</t>
+          <t xml:space="preserve">0</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">C1</t>
+          <t xml:space="preserve">R20</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t xml:space="preserve">39.5mm</t>
+          <t xml:space="preserve">72mm</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t xml:space="preserve">25.5mm</t>
+          <t xml:space="preserve">55.81mm</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">270</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">U1</t>
+          <t xml:space="preserve">R16</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t xml:space="preserve">34mm</t>
+          <t xml:space="preserve">79mm</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t xml:space="preserve">114mm</t>
+          <t xml:space="preserve">47.81mm</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t xml:space="preserve">0</t>
+          <t xml:space="preserve">270</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">R64</t>
+          <t xml:space="preserve">R23</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t xml:space="preserve">34.19mm</t>
+          <t xml:space="preserve">64.19mm</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t xml:space="preserve">48mm</t>
+          <t xml:space="preserve">58mm</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -1714,27 +1714,27 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">R81</t>
+          <t xml:space="preserve">R64</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t xml:space="preserve">63.5mm</t>
+          <t xml:space="preserve">34.19mm</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t xml:space="preserve">44.81mm</t>
+          <t xml:space="preserve">48mm</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t xml:space="preserve">Top</t>
+          <t xml:space="preserve">Bottom</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t xml:space="preserve">270</t>
+          <t xml:space="preserve">180</t>
         </is>
       </c>
     </row>
